--- a/output/pdf_financials_xlsx/AML.xlsx
+++ b/output/pdf_financials_xlsx/AML.xlsx
@@ -40372,10 +40372,10 @@
         </is>
       </c>
       <c r="E346" s="5" t="n">
-        <v>0.001203</v>
+        <v>-0.001203</v>
       </c>
       <c r="F346" s="5" t="n">
-        <v>0.21075</v>
+        <v>-0.21075</v>
       </c>
       <c r="G346" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/AML.xlsx
+++ b/output/pdf_financials_xlsx/AML.xlsx
@@ -922,13 +922,13 @@
         <v>0.30337</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.098477</v>
+        <v>0.214372</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.123675</v>
+        <v>0.187835</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0.105931</v>
+        <v>0.206001</v>
       </c>
       <c r="P10" s="3" t="n">
         <v>0.095527</v>
@@ -977,13 +977,13 @@
         <v>-0.30337</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>-0.098477</v>
+        <v>-0.214372</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>-0.123675</v>
+        <v>-0.187835</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>-0.105931</v>
+        <v>-0.206001</v>
       </c>
       <c r="P11" s="3" t="n">
         <v>-0.095527</v>
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>2e-06</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0</v>
@@ -1916,7 +1916,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.203287</v>
+        <v>-0.203289</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-0.317921</v>
@@ -2026,7 +2026,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.203287</v>
+        <v>-0.203289</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-0.314485</v>
@@ -2317,7 +2317,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.015961</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0.015961</v>
@@ -2335,34 +2335,34 @@
         <v>0.390872</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.034319</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.002289</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>2.119547</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>3.208271</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.899945</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.318645</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.037897</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.035608</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.017963</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.108078</v>
       </c>
     </row>
     <row r="35">
@@ -2427,7 +2427,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.015961</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0.015961</v>
@@ -2445,34 +2445,34 @@
         <v>0.390872</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.034319</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.002289</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>2.119547</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>3.208271</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.899945</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.318645</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.037897</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.035608</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.017963</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.108078</v>
       </c>
     </row>
     <row r="37">
@@ -3087,7 +3087,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.015961</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>0</v>
@@ -3105,34 +3105,34 @@
         <v>0.015657</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.044645</v>
+        <v>0.010326</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.011289</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>2.128047</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>3.216417</v>
+        <v>0.008146</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.913301</v>
+        <v>0.013356</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.329459</v>
+        <v>0.010814</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.05134</v>
+        <v>0.013443</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.067076</v>
+        <v>0.031468</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.107535</v>
+        <v>0.089572</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.261759</v>
+        <v>0.153681</v>
       </c>
     </row>
     <row r="49">
@@ -8124,7 +8124,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -14396,7 +14396,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E70" s="5" t="n">
@@ -29178,7 +29178,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -30348,7 +30348,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -30407,13 +30407,13 @@
         </is>
       </c>
       <c r="P241" s="5" t="n">
-        <v>-0.214372</v>
+        <v>0.214372</v>
       </c>
       <c r="Q241" s="5" t="n">
-        <v>-0.187835</v>
+        <v>0.187835</v>
       </c>
       <c r="R241" s="5" t="n">
-        <v>-0.206001</v>
+        <v>0.206001</v>
       </c>
       <c r="S241" t="inlineStr">
         <is>
@@ -37934,7 +37934,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E321" s="5" t="n">

--- a/output/pdf_financials_xlsx/AML.xlsx
+++ b/output/pdf_financials_xlsx/AML.xlsx
@@ -840,22 +840,22 @@
         <v>0.10069</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.539194</v>
+        <v>0.638786</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0.62234</v>
+        <v>0.7476739999999999</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.442098</v>
+        <v>0.5325530000000001</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.297724</v>
+        <v>0.363687</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>0.222041</v>
+        <v>0.223193</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>0.179201</v>
+        <v>0.184575</v>
       </c>
       <c r="J9" s="3" t="n">
         <v>0.07949299999999999</v>
@@ -904,13 +904,13 @@
         <v>0.888162</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.372172</v>
+        <v>0.438135</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.251961</v>
+        <v>0.253113</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.234863</v>
+        <v>0.240237</v>
       </c>
       <c r="J10" s="3" t="n">
         <v>0.170818</v>
@@ -959,13 +959,13 @@
         <v>-0.888162</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-0.372172</v>
+        <v>-0.438135</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>-0.251961</v>
+        <v>-0.253113</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>-0.234863</v>
+        <v>-0.240237</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>-0.170818</v>
@@ -32138,7 +32138,11 @@
           <t>Rent and occupancy costs</t>
         </is>
       </c>
-      <c r="D260" t="inlineStr"/>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E260" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/AML.xlsx
+++ b/output/pdf_financials_xlsx/AML.xlsx
@@ -757,19 +757,19 @@
         <v>0.07069599999999999</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.02609</v>
+        <v>0.02984</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0.048179</v>
+        <v>0.052229</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>0.032582</v>
+        <v>0.036551</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>0.022862</v>
+        <v>0.028048</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.023229</v>
+        <v>0.02862</v>
       </c>
     </row>
     <row r="8">
@@ -931,10 +931,10 @@
         <v>0.206001</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0.095527</v>
+        <v>0.100713</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0.09606099999999999</v>
+        <v>0.101452</v>
       </c>
     </row>
     <row r="11">
@@ -986,10 +986,10 @@
         <v>-0.206001</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>-0.095527</v>
+        <v>-0.100713</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>-0.09606099999999999</v>
+        <v>-0.101452</v>
       </c>
     </row>
     <row r="12">
@@ -6040,7 +6040,7 @@
         <v>-0.021597</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>-0.12291</v>
+        <v>-0.057631</v>
       </c>
       <c r="E101" s="3" t="n">
         <v>0.111986</v>
@@ -6315,7 +6315,7 @@
         <v>0.07670200000000001</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>-0.534075</v>
+        <v>-0.468796</v>
       </c>
       <c r="E106" s="3" t="n">
         <v>-0.005258</v>
@@ -6590,10 +6590,10 @@
         <v>-0.029723</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.062971</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.01228</v>
       </c>
       <c r="F111" s="3" t="n">
         <v>0</v>
@@ -6611,13 +6611,13 @@
         <v>0</v>
       </c>
       <c r="K111" s="3" t="n">
-        <v>0</v>
+        <v>-0.002069</v>
       </c>
       <c r="L111" s="3" t="n">
-        <v>0</v>
+        <v>-0.000728</v>
       </c>
       <c r="M111" s="3" t="n">
-        <v>0</v>
+        <v>-0.002899</v>
       </c>
       <c r="N111" s="3" t="n">
         <v>0</v>
@@ -7887,10 +7887,10 @@
         <v>-0.029723</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.062971</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.01228</v>
       </c>
       <c r="F134" s="3" t="n">
         <v>0</v>
@@ -7908,13 +7908,13 @@
         <v>0</v>
       </c>
       <c r="K134" s="3" t="n">
-        <v>0</v>
+        <v>-0.002069</v>
       </c>
       <c r="L134" s="3" t="n">
-        <v>0</v>
+        <v>-0.000728</v>
       </c>
       <c r="M134" s="3" t="n">
-        <v>0</v>
+        <v>-0.002899</v>
       </c>
       <c r="N134" s="3" t="n">
         <v>0</v>
@@ -7942,10 +7942,10 @@
         <v>-0.244018</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-2.013166</v>
+        <v>-2.076137</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-1.28012</v>
+        <v>-1.2924</v>
       </c>
       <c r="F135" s="3" t="n">
         <v>-0.5465950000000001</v>
@@ -7963,13 +7963,13 @@
         <v>-0.276175</v>
       </c>
       <c r="K135" s="3" t="n">
-        <v>-0.325723</v>
+        <v>-0.327792</v>
       </c>
       <c r="L135" s="3" t="n">
-        <v>-0.210856</v>
+        <v>-0.211584</v>
       </c>
       <c r="M135" s="3" t="n">
-        <v>-0.171594</v>
+        <v>-0.174493</v>
       </c>
       <c r="N135" s="3" t="n">
         <v>-0.16355</v>
@@ -17398,7 +17398,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
           <t>-</t>
@@ -19298,7 +19302,11 @@
           <t>Proceeds from share issuances (net)</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr"/>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E124" t="inlineStr">
         <is>
           <t>-</t>
@@ -20326,7 +20334,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E135" t="inlineStr">
         <is>
           <t>-</t>
@@ -21348,7 +21360,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr"/>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E146" t="inlineStr">
         <is>
           <t>-</t>
@@ -22108,7 +22124,11 @@
           <t>Writedown of GST receivable</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr"/>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E154" t="inlineStr">
         <is>
           <t>-</t>
@@ -23258,7 +23278,11 @@
           <t>Writedown of GST receivable 65,279</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr"/>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E166" t="inlineStr">
         <is>
           <t>-</t>
@@ -29082,7 +29106,11 @@
           <t>Directors’ fees (Note 7)</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr"/>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E227" t="inlineStr">
         <is>
           <t>-</t>
@@ -29980,7 +30008,11 @@
           <t>Directors fees (Note 7)</t>
         </is>
       </c>
-      <c r="D237" t="inlineStr"/>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E237" t="inlineStr">
         <is>
           <t>-</t>
